--- a/data/trans_dic/IP19C05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,32 +788,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,45</t>
+          <t>1,3; 7,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,48</t>
+          <t>0,48; 4,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,49; 4,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,42</t>
+          <t>0,31; 2,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,77</t>
+          <t>1,16; 4,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,83</t>
+          <t>0,54; 2,87</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,95</t>
+          <t>0,37; 3,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,74</t>
+          <t>1,03; 6,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 8,21</t>
+          <t>2,12; 7,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,78</t>
+          <t>0,91; 5,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,46</t>
+          <t>1,25; 7,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,33</t>
+          <t>0,37; 2,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,51</t>
+          <t>1,48; 4,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,4</t>
+          <t>2,34; 6,33</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,09</t>
+          <t>0,36; 2,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,47</t>
+          <t>1,42; 4,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,15</t>
+          <t>1,36; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,19</t>
+          <t>0,36; 2,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,1</t>
+          <t>0,78; 3,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,1</t>
+          <t>0,8; 3,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,74</t>
+          <t>0,52; 1,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,18</t>
+          <t>1,37; 3,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,12</t>
+          <t>1,37; 3,15</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2611</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2642</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4109</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3984</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4599</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3768</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4536</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2770</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6620</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3182</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1630; 9529</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>715; 6685</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5547</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>645; 5745</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4907</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>645; 5681</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2989; 11885</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1612; 8569</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4307</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6334</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3414</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7721</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11157</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>600; 5809</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1521; 9457</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3069; 11411</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4437</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1289; 7862</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1690; 9504</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1239; 8012</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4286; 13018</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>6560; 17736</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3387</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9286</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6918</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>15504</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>15257</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1266; 7840</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5024; 15210</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4915; 15038</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1317; 7925</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2840; 11182</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2928; 11394</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3691; 12639</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9897; 23270</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>10024; 23039</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Edad-trans_dic.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 4,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,62</t>
+          <t>1,58; 7,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,49</t>
+          <t>0,49; 4,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,35</t>
+          <t>0,49; 4,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,77</t>
+          <t>0,31; 2,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,62</t>
+          <t>1,18; 4,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,87</t>
+          <t>0,63; 2,92</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,55</t>
+          <t>0,37; 3,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,39</t>
+          <t>1,03; 5,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,86</t>
+          <t>2,2; 8,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,57</t>
+          <t>0,92; 5,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,03</t>
+          <t>1,24; 7,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,38</t>
+          <t>0,38; 2,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,5</t>
+          <t>1,44; 4,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,33</t>
+          <t>2,29; 6,37</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,23</t>
+          <t>0,35; 2,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,3</t>
+          <t>1,49; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,15</t>
+          <t>1,45; 4,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,19</t>
+          <t>0,36; 2,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,06</t>
+          <t>0,78; 3,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,1</t>
+          <t>0,78; 3,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,77</t>
+          <t>0,49; 1,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,23</t>
+          <t>1,35; 3,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,15</t>
+          <t>1,24; 3,15</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2611</t>
+          <t>0; 3029</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2642</t>
+          <t>0; 2638</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4109</t>
+          <t>0; 3830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3984</t>
+          <t>0; 3249</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4599</t>
+          <t>0; 4715</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3768</t>
+          <t>0; 4549</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3182</t>
+          <t>0; 3241</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1630; 9529</t>
+          <t>1972; 8985</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>715; 6685</t>
+          <t>731; 6822</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5547</t>
+          <t>0; 5612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>645; 5745</t>
+          <t>648; 5812</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4907</t>
+          <t>0; 4670</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>645; 5681</t>
+          <t>641; 6001</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2989; 11885</t>
+          <t>3031; 11735</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1612; 8569</t>
+          <t>1884; 8713</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>600; 5809</t>
+          <t>598; 5651</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1521; 9457</t>
+          <t>1519; 8670</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3069; 11411</t>
+          <t>3190; 12613</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4437</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1289; 7862</t>
+          <t>1295; 7614</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1690; 9504</t>
+          <t>1677; 9796</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1239; 8012</t>
+          <t>1269; 7855</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4286; 13018</t>
+          <t>4151; 13083</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6560; 17736</t>
+          <t>6433; 17865</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1266; 7840</t>
+          <t>1237; 7453</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5024; 15210</t>
+          <t>5259; 15848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4915; 15038</t>
+          <t>5262; 16245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1317; 7925</t>
+          <t>1299; 8508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2840; 11182</t>
+          <t>2848; 11619</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2928; 11394</t>
+          <t>2859; 11704</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3691; 12639</t>
+          <t>3505; 12640</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9897; 23270</t>
+          <t>9716; 22836</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10024; 23039</t>
+          <t>9037; 23031</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C05-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 4,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,63%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,86%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,18</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,58</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,4</t>
+          <t>1,26; 7,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,49; 4,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,93</t>
+          <t>0,31; 3,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,56</t>
+          <t>1,3; 4,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,92</t>
+          <t>0,45; 2,83</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,91%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,36%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,46</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,86</t>
+          <t>0,91; 5,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,69</t>
+          <t>1,25; 7,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,37; 3,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,39</t>
+          <t>0,99; 5,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,24</t>
+          <t>1,86; 8,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,33</t>
+          <t>0,37; 2,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,53</t>
+          <t>1,32; 4,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,37</t>
+          <t>2,3; 6,4</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,12</t>
+          <t>0,37; 2,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,48</t>
+          <t>0,77; 3,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,48</t>
+          <t>0,66; 3,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,35</t>
+          <t>0,36; 2,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,17</t>
+          <t>1,51; 4,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,18</t>
+          <t>1,4; 4,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,77</t>
+          <t>0,48; 1,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,17</t>
+          <t>1,42; 3,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,15</t>
+          <t>1,35; 3,12</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1527,27 +1527,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>443</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3029</t>
+          <t>0; 3440</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2638</t>
+          <t>0; 3609</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3830</t>
+          <t>0; 3257</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3249</t>
+          <t>0; 2714</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4715</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4549</t>
+          <t>0; 4022</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>4536</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2770</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1330</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3241</t>
+          <t>0; 6304</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1972; 8985</t>
+          <t>0; 5512</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>731; 6822</t>
+          <t>0; 3983</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5612</t>
+          <t>0; 3207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>648; 5812</t>
+          <t>1580; 9319</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4670</t>
+          <t>730; 6671</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>641; 6001</t>
+          <t>639; 7001</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3031; 11735</t>
+          <t>3346; 12255</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1884; 8713</t>
+          <t>1330; 8445</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3414</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2103</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4307</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6334</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1286</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3414</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4823</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>598; 5651</t>
+          <t>0; 4512</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1519; 8670</t>
+          <t>1281; 8154</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3190; 12613</t>
+          <t>1689; 10093</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4605</t>
+          <t>599; 6462</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1295; 7614</t>
+          <t>1462; 8495</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1677; 9796</t>
+          <t>2698; 11908</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1269; 7855</t>
+          <t>1235; 7855</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4151; 13083</t>
+          <t>3817; 13044</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6433; 17865</t>
+          <t>6441; 17948</t>
         </is>
       </c>
     </row>
@@ -1968,27 +1968,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>3387</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>9286</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>9104</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6218</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6153</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1237; 7453</t>
+          <t>1331; 7935</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5259; 15848</t>
+          <t>2800; 11351</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5262; 16245</t>
+          <t>2440; 11413</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1299; 8508</t>
+          <t>1255; 7349</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2848; 11619</t>
+          <t>5329; 15840</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2859; 11704</t>
+          <t>5089; 15050</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3505; 12640</t>
+          <t>3427; 12413</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9716; 22836</t>
+          <t>10200; 22903</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9037; 23031</t>
+          <t>9859; 22801</t>
         </is>
       </c>
     </row>
